--- a/data/trans_bre/P1802_2016_2023-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P1802_2016_2023-Habitat-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,84</t>
+          <t>3,01</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>21,87%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,85; 8,68</t>
+          <t>0,5; 8,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 6,41</t>
+          <t>-0,27; 6,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,24; 80,52</t>
+          <t>2,09; 74,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 52,84</t>
+          <t>-2,4; 50,51</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-16,88</t>
+          <t>2,03</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-54,09%</t>
+          <t>15,88%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,08; 7,74</t>
+          <t>0,97; 7,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-47,82; 1,64</t>
+          <t>-0,94; 4,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,17; 53,16</t>
+          <t>5,25; 54,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-78,21; 12,82</t>
+          <t>-6,48; 43,06</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>6,46</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>47,72%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 8,91</t>
+          <t>1,41; 9,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 5,62</t>
+          <t>2,94; 10,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,58; 76,59</t>
+          <t>9,22; 78,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-49,56; 41,77</t>
+          <t>18,89; 87,98</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,14</t>
+          <t>3,07</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>15,47%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 7,42</t>
+          <t>0,59; 7,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 4,84</t>
+          <t>-0,17; 6,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,09; 59,35</t>
+          <t>3,7; 62,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,8; 26,04</t>
+          <t>-0,83; 38,51</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-4,69</t>
+          <t>3,63</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-21,43%</t>
+          <t>23,98%</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,61; 6,2</t>
+          <t>2,75; 6,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-23,4; 2,08</t>
+          <t>1,89; 5,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17,14; 46,19</t>
+          <t>17,93; 47,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-59,73; 13,29</t>
+          <t>11,53; 37,62</t>
         </is>
       </c>
     </row>
